--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N52_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N52_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.45475260288839</v>
+        <v>8.686397297969364</v>
       </c>
       <c r="D2" t="n">
-        <v>56.00555808907868</v>
+        <v>9.100903189475286</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6028023872330337</v>
+        <v>0.09795538792536806</v>
       </c>
       <c r="F2" t="n">
-        <v>3.271007574481569</v>
+        <v>0.5315387308532546</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>54.66035737735446</v>
+        <v>8.8823080738201</v>
       </c>
       <c r="D3" t="n">
-        <v>49.46354294011554</v>
+        <v>8.037825727768777</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6028023872330337</v>
+        <v>0.09795538792536806</v>
       </c>
       <c r="F3" t="n">
-        <v>3.271007574481569</v>
+        <v>0.5315387308532546</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
